--- a/tests/systeem_testen/224/results/df_beta_limit_states.xlsx
+++ b/tests/systeem_testen/224/results/df_beta_limit_states.xlsx
@@ -486,13 +486,13 @@
         </is>
       </c>
       <c r="F2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>8.779999999999999</v>
+        <v>16.54</v>
       </c>
       <c r="H2" t="n">
-        <v>7.913435684995362e-19</v>
+        <v>1.022289860523464e-61</v>
       </c>
     </row>
     <row r="3">
@@ -516,13 +516,13 @@
         </is>
       </c>
       <c r="F3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>9.550000000000001</v>
+        <v>20.84</v>
       </c>
       <c r="H3" t="n">
-        <v>6.185997414781388e-22</v>
+        <v>9.566741312138489e-97</v>
       </c>
     </row>
     <row r="4">
@@ -549,10 +549,10 @@
         <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>-6.16</v>
+        <v>2.44</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9999999996357465</v>
+        <v>0.007260358961209182</v>
       </c>
     </row>
     <row r="5">
@@ -576,13 +576,13 @@
         </is>
       </c>
       <c r="F5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>8.779999999999999</v>
+        <v>16.46</v>
       </c>
       <c r="H5" t="n">
-        <v>7.913435684995362e-19</v>
+        <v>3.518773872523342e-61</v>
       </c>
     </row>
     <row r="6">
@@ -606,13 +606,13 @@
         </is>
       </c>
       <c r="F6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>9.550000000000001</v>
+        <v>20.54</v>
       </c>
       <c r="H6" t="n">
-        <v>6.185997414781388e-22</v>
+        <v>4.851656212467633e-94</v>
       </c>
     </row>
     <row r="7">
@@ -639,10 +639,10 @@
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>-6.16</v>
+        <v>2.2</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9999999996357465</v>
+        <v>0.01406246216972141</v>
       </c>
     </row>
     <row r="8">
@@ -666,13 +666,13 @@
         </is>
       </c>
       <c r="F8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>8.779999999999999</v>
+        <v>14.65</v>
       </c>
       <c r="H8" t="n">
-        <v>7.913435684995362e-19</v>
+        <v>6.337972154182476e-49</v>
       </c>
     </row>
     <row r="9">
@@ -696,13 +696,13 @@
         </is>
       </c>
       <c r="F9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>9.550000000000001</v>
+        <v>16.44</v>
       </c>
       <c r="H9" t="n">
-        <v>6.185997414781388e-22</v>
+        <v>4.690144863239992e-61</v>
       </c>
     </row>
     <row r="10">
@@ -729,10 +729,10 @@
         <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>-6.16</v>
+        <v>0.66</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9999999996357465</v>
+        <v>0.2547649433411128</v>
       </c>
     </row>
     <row r="11">
@@ -756,13 +756,13 @@
         </is>
       </c>
       <c r="F11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>8.779999999999999</v>
+        <v>12.83</v>
       </c>
       <c r="H11" t="n">
-        <v>7.913435684995362e-19</v>
+        <v>5.891129137286337e-38</v>
       </c>
     </row>
     <row r="12">
@@ -786,13 +786,13 @@
         </is>
       </c>
       <c r="F12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>9.550000000000001</v>
+        <v>14.09</v>
       </c>
       <c r="H12" t="n">
-        <v>6.185997414781388e-22</v>
+        <v>2.253730339103421e-45</v>
       </c>
     </row>
     <row r="13">
@@ -819,10 +819,10 @@
         <v>1</v>
       </c>
       <c r="G13" t="n">
-        <v>-6.16</v>
+        <v>-0.82</v>
       </c>
       <c r="H13" t="n">
-        <v>0.9999999996357465</v>
+        <v>0.7948437968216684</v>
       </c>
     </row>
     <row r="14">
@@ -846,13 +846,13 @@
         </is>
       </c>
       <c r="F14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>8.779999999999999</v>
+        <v>16.25</v>
       </c>
       <c r="H14" t="n">
-        <v>7.913435684995362e-19</v>
+        <v>1.093769464632315e-59</v>
       </c>
     </row>
     <row r="15">
@@ -876,13 +876,13 @@
         </is>
       </c>
       <c r="F15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>9.550000000000001</v>
+        <v>19.78</v>
       </c>
       <c r="H15" t="n">
-        <v>6.185997414781388e-22</v>
+        <v>2.031300003832916e-87</v>
       </c>
     </row>
     <row r="16">
@@ -909,10 +909,10 @@
         <v>1</v>
       </c>
       <c r="G16" t="n">
-        <v>-6.16</v>
+        <v>1.67</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9999999996357465</v>
+        <v>0.04731893673573939</v>
       </c>
     </row>
     <row r="17">
@@ -936,13 +936,13 @@
         </is>
       </c>
       <c r="F17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>8.779999999999999</v>
+        <v>16.41</v>
       </c>
       <c r="H17" t="n">
-        <v>7.913435684995362e-19</v>
+        <v>8.454637351506728e-61</v>
       </c>
     </row>
     <row r="18">
@@ -966,13 +966,13 @@
         </is>
       </c>
       <c r="F18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>9.550000000000001</v>
+        <v>20.37</v>
       </c>
       <c r="H18" t="n">
-        <v>6.185997414781388e-22</v>
+        <v>1.622592202406906e-92</v>
       </c>
     </row>
     <row r="19">
@@ -999,10 +999,10 @@
         <v>1</v>
       </c>
       <c r="G19" t="n">
-        <v>-6.16</v>
+        <v>1.97</v>
       </c>
       <c r="H19" t="n">
-        <v>0.9999999996357465</v>
+        <v>0.02436420159636477</v>
       </c>
     </row>
     <row r="20">
@@ -1026,13 +1026,13 @@
         </is>
       </c>
       <c r="F20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>8.779999999999999</v>
+        <v>16.41</v>
       </c>
       <c r="H20" t="n">
-        <v>7.913435684995362e-19</v>
+        <v>7.699029657964296e-61</v>
       </c>
     </row>
     <row r="21">
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="F21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>9.550000000000001</v>
+        <v>20.39</v>
       </c>
       <c r="H21" t="n">
-        <v>6.185997414781388e-22</v>
+        <v>1.045338813820739e-92</v>
       </c>
     </row>
     <row r="22">
@@ -1089,10 +1089,10 @@
         <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>-6.16</v>
+        <v>1.99</v>
       </c>
       <c r="H22" t="n">
-        <v>0.9999999996357465</v>
+        <v>0.02320514977244344</v>
       </c>
     </row>
     <row r="23">
@@ -1116,13 +1116,13 @@
         </is>
       </c>
       <c r="F23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>8.779999999999999</v>
+        <v>14.8</v>
       </c>
       <c r="H23" t="n">
-        <v>7.913435684995362e-19</v>
+        <v>6.899850316168235e-50</v>
       </c>
     </row>
     <row r="24">
@@ -1146,13 +1146,13 @@
         </is>
       </c>
       <c r="F24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>9.550000000000001</v>
+        <v>16.67</v>
       </c>
       <c r="H24" t="n">
-        <v>6.185997414781388e-22</v>
+        <v>1.016583930550708e-62</v>
       </c>
     </row>
     <row r="25">
@@ -1179,10 +1179,10 @@
         <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>-6.16</v>
+        <v>0.91</v>
       </c>
       <c r="H25" t="n">
-        <v>0.9999999996357465</v>
+        <v>0.1822686661913348</v>
       </c>
     </row>
     <row r="26">
@@ -1206,13 +1206,13 @@
         </is>
       </c>
       <c r="F26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>8.779999999999999</v>
+        <v>16.28</v>
       </c>
       <c r="H26" t="n">
-        <v>7.913435684995362e-19</v>
+        <v>7.357641497274017e-60</v>
       </c>
     </row>
     <row r="27">
@@ -1236,13 +1236,13 @@
         </is>
       </c>
       <c r="F27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>9.550000000000001</v>
+        <v>19.89</v>
       </c>
       <c r="H27" t="n">
-        <v>6.185997414781388e-22</v>
+        <v>2.344796345938716e-88</v>
       </c>
     </row>
     <row r="28">
@@ -1269,10 +1269,10 @@
         <v>1</v>
       </c>
       <c r="G28" t="n">
-        <v>-6.16</v>
+        <v>1.73</v>
       </c>
       <c r="H28" t="n">
-        <v>0.9999999996357465</v>
+        <v>0.04204215547125202</v>
       </c>
     </row>
     <row r="29">
@@ -1296,13 +1296,13 @@
         </is>
       </c>
       <c r="F29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>8.779999999999999</v>
+        <v>16.55</v>
       </c>
       <c r="H29" t="n">
-        <v>7.913435684995362e-19</v>
+        <v>7.672997821500475e-62</v>
       </c>
     </row>
     <row r="30">
@@ -1326,13 +1326,13 @@
         </is>
       </c>
       <c r="F30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>9.550000000000001</v>
+        <v>20.95</v>
       </c>
       <c r="H30" t="n">
-        <v>6.185997414781388e-22</v>
+        <v>9.999764509932361e-98</v>
       </c>
     </row>
     <row r="31">
@@ -1359,10 +1359,10 @@
         <v>1</v>
       </c>
       <c r="G31" t="n">
-        <v>-6.16</v>
+        <v>2.69</v>
       </c>
       <c r="H31" t="n">
-        <v>0.9999999996357465</v>
+        <v>0.003560833039414419</v>
       </c>
     </row>
     <row r="32">
@@ -1386,13 +1386,13 @@
         </is>
       </c>
       <c r="F32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>8.779999999999999</v>
+        <v>16.53</v>
       </c>
       <c r="H32" t="n">
-        <v>7.913435684995362e-19</v>
+        <v>1.173910937191186e-61</v>
       </c>
     </row>
     <row r="33">
@@ -1416,13 +1416,13 @@
         </is>
       </c>
       <c r="F33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>9.550000000000001</v>
+        <v>20.84</v>
       </c>
       <c r="H33" t="n">
-        <v>6.185997414781388e-22</v>
+        <v>9.404872388359379e-97</v>
       </c>
     </row>
     <row r="34">
@@ -1449,10 +1449,10 @@
         <v>1</v>
       </c>
       <c r="G34" t="n">
-        <v>-6.16</v>
+        <v>2.77</v>
       </c>
       <c r="H34" t="n">
-        <v>0.9999999996357465</v>
+        <v>0.002835546510702765</v>
       </c>
     </row>
     <row r="35">
@@ -1476,13 +1476,13 @@
         </is>
       </c>
       <c r="F35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>8.779999999999999</v>
+        <v>16.32</v>
       </c>
       <c r="H35" t="n">
-        <v>7.913435684995362e-19</v>
+        <v>3.715209399497063e-60</v>
       </c>
     </row>
     <row r="36">
@@ -1506,13 +1506,13 @@
         </is>
       </c>
       <c r="F36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>9.550000000000001</v>
+        <v>20.06</v>
       </c>
       <c r="H36" t="n">
-        <v>6.185997414781388e-22</v>
+        <v>7.714785317117291e-90</v>
       </c>
     </row>
     <row r="37">
@@ -1539,10 +1539,10 @@
         <v>1</v>
       </c>
       <c r="G37" t="n">
-        <v>-6.16</v>
+        <v>1.81</v>
       </c>
       <c r="H37" t="n">
-        <v>0.9999999996357465</v>
+        <v>0.03483302189453291</v>
       </c>
     </row>
     <row r="38">
@@ -1566,13 +1566,13 @@
         </is>
       </c>
       <c r="F38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>8.779999999999999</v>
+        <v>16.39</v>
       </c>
       <c r="H38" t="n">
-        <v>7.913435684995362e-19</v>
+        <v>1.054562259969648e-60</v>
       </c>
     </row>
     <row r="39">
@@ -1596,13 +1596,13 @@
         </is>
       </c>
       <c r="F39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>9.550000000000001</v>
+        <v>20.34</v>
       </c>
       <c r="H39" t="n">
-        <v>6.185997414781388e-22</v>
+        <v>2.651930166377981e-92</v>
       </c>
     </row>
     <row r="40">
@@ -1629,10 +1629,10 @@
         <v>1</v>
       </c>
       <c r="G40" t="n">
-        <v>-6.16</v>
+        <v>2.52</v>
       </c>
       <c r="H40" t="n">
-        <v>0.9999999996357465</v>
+        <v>0.005822293712397717</v>
       </c>
     </row>
     <row r="41">
@@ -1656,13 +1656,13 @@
         </is>
       </c>
       <c r="F41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>8.779999999999999</v>
+        <v>16.4</v>
       </c>
       <c r="H41" t="n">
-        <v>7.913435684995362e-19</v>
+        <v>9.247511440709148e-61</v>
       </c>
     </row>
     <row r="42">
@@ -1686,13 +1686,13 @@
         </is>
       </c>
       <c r="F42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>9.550000000000001</v>
+        <v>20.36</v>
       </c>
       <c r="H42" t="n">
-        <v>6.185997414781388e-22</v>
+        <v>1.709789952492868e-92</v>
       </c>
     </row>
     <row r="43">
@@ -1719,10 +1719,10 @@
         <v>1</v>
       </c>
       <c r="G43" t="n">
-        <v>-6.16</v>
+        <v>2.59</v>
       </c>
       <c r="H43" t="n">
-        <v>0.9999999996357465</v>
+        <v>0.004792742188965333</v>
       </c>
     </row>
     <row r="44">
@@ -1746,13 +1746,13 @@
         </is>
       </c>
       <c r="F44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>8.779999999999999</v>
+        <v>16.19</v>
       </c>
       <c r="H44" t="n">
-        <v>7.913435684995362e-19</v>
+        <v>2.981887158786519e-59</v>
       </c>
     </row>
     <row r="45">
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="F45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>9.550000000000001</v>
+        <v>19.63</v>
       </c>
       <c r="H45" t="n">
-        <v>6.185997414781388e-22</v>
+        <v>4.226635707150987e-86</v>
       </c>
     </row>
     <row r="46">
@@ -1809,10 +1809,10 @@
         <v>1</v>
       </c>
       <c r="G46" t="n">
-        <v>-6.16</v>
+        <v>1.95</v>
       </c>
       <c r="H46" t="n">
-        <v>0.9999999996357465</v>
+        <v>0.02538134741859991</v>
       </c>
     </row>
     <row r="47">
@@ -1836,13 +1836,13 @@
         </is>
       </c>
       <c r="F47" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>8.779999999999999</v>
+        <v>16.16</v>
       </c>
       <c r="H47" t="n">
-        <v>7.913435684995362e-19</v>
+        <v>5.174224183396022e-59</v>
       </c>
     </row>
     <row r="48">
@@ -1866,13 +1866,13 @@
         </is>
       </c>
       <c r="F48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>9.550000000000001</v>
+        <v>19.52</v>
       </c>
       <c r="H48" t="n">
-        <v>6.185997414781388e-22</v>
+        <v>3.55508338533629e-85</v>
       </c>
     </row>
     <row r="49">
@@ -1899,10 +1899,10 @@
         <v>1</v>
       </c>
       <c r="G49" t="n">
-        <v>-6.16</v>
+        <v>1.52</v>
       </c>
       <c r="H49" t="n">
-        <v>0.9999999996357465</v>
+        <v>0.06369849711450008</v>
       </c>
     </row>
     <row r="50">
@@ -1926,13 +1926,13 @@
         </is>
       </c>
       <c r="F50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>8.779999999999999</v>
+        <v>16.17</v>
       </c>
       <c r="H50" t="n">
-        <v>7.913435684995362e-19</v>
+        <v>4.000207845700471e-59</v>
       </c>
     </row>
     <row r="51">
@@ -1956,13 +1956,13 @@
         </is>
       </c>
       <c r="F51" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>9.550000000000001</v>
+        <v>19.58</v>
       </c>
       <c r="H51" t="n">
-        <v>6.185997414781388e-22</v>
+        <v>1.255192676577688e-85</v>
       </c>
     </row>
     <row r="52">
@@ -1989,10 +1989,10 @@
         <v>1</v>
       </c>
       <c r="G52" t="n">
-        <v>-6.16</v>
+        <v>2.01</v>
       </c>
       <c r="H52" t="n">
-        <v>0.9999999996357465</v>
+        <v>0.02221787456837669</v>
       </c>
     </row>
     <row r="53">
@@ -2016,13 +2016,13 @@
         </is>
       </c>
       <c r="F53" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>8.779999999999999</v>
+        <v>16.07</v>
       </c>
       <c r="H53" t="n">
-        <v>7.913435684995362e-19</v>
+        <v>1.977966285458293e-58</v>
       </c>
     </row>
     <row r="54">
@@ -2046,13 +2046,13 @@
         </is>
       </c>
       <c r="F54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G54" t="n">
-        <v>9.550000000000001</v>
+        <v>19.27</v>
       </c>
       <c r="H54" t="n">
-        <v>6.185997414781388e-22</v>
+        <v>4.689057070233716e-83</v>
       </c>
     </row>
     <row r="55">
@@ -2079,10 +2079,10 @@
         <v>1</v>
       </c>
       <c r="G55" t="n">
-        <v>-6.16</v>
+        <v>2.16</v>
       </c>
       <c r="H55" t="n">
-        <v>0.9999999996357465</v>
+        <v>0.01531928766753382</v>
       </c>
     </row>
     <row r="56">
@@ -2106,13 +2106,13 @@
         </is>
       </c>
       <c r="F56" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>8.779999999999999</v>
+        <v>12.58</v>
       </c>
       <c r="H56" t="n">
-        <v>7.913435684995362e-19</v>
+        <v>1.434692229494124e-36</v>
       </c>
     </row>
     <row r="57">
@@ -2136,13 +2136,13 @@
         </is>
       </c>
       <c r="F57" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>9.550000000000001</v>
+        <v>13.8</v>
       </c>
       <c r="H57" t="n">
-        <v>6.185997414781388e-22</v>
+        <v>1.288457850869191e-43</v>
       </c>
     </row>
     <row r="58">
@@ -2169,10 +2169,10 @@
         <v>1</v>
       </c>
       <c r="G58" t="n">
-        <v>-6.16</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="H58" t="n">
-        <v>0.9999999996357465</v>
+        <v>0.7535363053419541</v>
       </c>
     </row>
     <row r="59">
@@ -2196,13 +2196,13 @@
         </is>
       </c>
       <c r="F59" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G59" t="n">
-        <v>8.779999999999999</v>
+        <v>12.52</v>
       </c>
       <c r="H59" t="n">
-        <v>7.913435684995362e-19</v>
+        <v>3.055181167209931e-36</v>
       </c>
     </row>
     <row r="60">
@@ -2226,13 +2226,13 @@
         </is>
       </c>
       <c r="F60" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G60" t="n">
-        <v>9.550000000000001</v>
+        <v>13.73</v>
       </c>
       <c r="H60" t="n">
-        <v>6.185997414781388e-22</v>
+        <v>3.478065297135899e-43</v>
       </c>
     </row>
     <row r="61">
@@ -2259,10 +2259,10 @@
         <v>1</v>
       </c>
       <c r="G61" t="n">
-        <v>-6.16</v>
+        <v>-0.2</v>
       </c>
       <c r="H61" t="n">
-        <v>0.9999999996357465</v>
+        <v>0.5780315476124758</v>
       </c>
     </row>
     <row r="62">
@@ -2286,13 +2286,13 @@
         </is>
       </c>
       <c r="F62" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G62" t="n">
-        <v>8.779999999999999</v>
+        <v>13.29</v>
       </c>
       <c r="H62" t="n">
-        <v>7.913435684995362e-19</v>
+        <v>1.2542622829436e-40</v>
       </c>
     </row>
     <row r="63">
@@ -2316,13 +2316,13 @@
         </is>
       </c>
       <c r="F63" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G63" t="n">
-        <v>9.550000000000001</v>
+        <v>14.68</v>
       </c>
       <c r="H63" t="n">
-        <v>6.185997414781388e-22</v>
+        <v>4.62871184246818e-49</v>
       </c>
     </row>
     <row r="64">
@@ -2349,10 +2349,10 @@
         <v>1</v>
       </c>
       <c r="G64" t="n">
-        <v>-6.16</v>
+        <v>-1.41</v>
       </c>
       <c r="H64" t="n">
-        <v>0.9999999996357465</v>
+        <v>0.9201452469392117</v>
       </c>
     </row>
     <row r="65">
@@ -2376,13 +2376,13 @@
         </is>
       </c>
       <c r="F65" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G65" t="n">
-        <v>8.779999999999999</v>
+        <v>16.21</v>
       </c>
       <c r="H65" t="n">
-        <v>7.913435684995362e-19</v>
+        <v>2.163315890118197e-59</v>
       </c>
     </row>
     <row r="66">
@@ -2409,10 +2409,10 @@
         <v>1</v>
       </c>
       <c r="G66" t="n">
-        <v>9.550000000000001</v>
+        <v>20.04</v>
       </c>
       <c r="H66" t="n">
-        <v>6.185997414781388e-22</v>
+        <v>1.198141059040024e-89</v>
       </c>
     </row>
     <row r="67">
@@ -2439,10 +2439,10 @@
         <v>1</v>
       </c>
       <c r="G67" t="n">
-        <v>-6.16</v>
+        <v>2.66</v>
       </c>
       <c r="H67" t="n">
-        <v>0.9999999996357465</v>
+        <v>0.003877849130846437</v>
       </c>
     </row>
     <row r="68">
@@ -2466,13 +2466,13 @@
         </is>
       </c>
       <c r="F68" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G68" t="n">
-        <v>8.779999999999999</v>
+        <v>16.25</v>
       </c>
       <c r="H68" t="n">
-        <v>7.913435684995362e-19</v>
+        <v>1.183569680975322e-59</v>
       </c>
     </row>
     <row r="69">
@@ -2499,10 +2499,10 @@
         <v>1</v>
       </c>
       <c r="G69" t="n">
-        <v>9.550000000000001</v>
+        <v>20.17</v>
       </c>
       <c r="H69" t="n">
-        <v>6.185997414781388e-22</v>
+        <v>8.847150988703814e-91</v>
       </c>
     </row>
     <row r="70">
@@ -2529,10 +2529,10 @@
         <v>1</v>
       </c>
       <c r="G70" t="n">
-        <v>-6.16</v>
+        <v>2.68</v>
       </c>
       <c r="H70" t="n">
-        <v>0.9999999996357465</v>
+        <v>0.003639115192831734</v>
       </c>
     </row>
     <row r="71">
@@ -2556,13 +2556,13 @@
         </is>
       </c>
       <c r="F71" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G71" t="n">
-        <v>8.779999999999999</v>
+        <v>17.19</v>
       </c>
       <c r="H71" t="n">
-        <v>7.913435684995362e-19</v>
+        <v>1.456109704171157e-66</v>
       </c>
     </row>
     <row r="72">
@@ -2589,10 +2589,10 @@
         <v>1</v>
       </c>
       <c r="G72" t="n">
-        <v>9.550000000000001</v>
+        <v>24.71</v>
       </c>
       <c r="H72" t="n">
-        <v>6.185997414781388e-22</v>
+        <v>3.888085122998408e-135</v>
       </c>
     </row>
     <row r="73">
@@ -2619,10 +2619,10 @@
         <v>1</v>
       </c>
       <c r="G73" t="n">
-        <v>-6.16</v>
+        <v>5.23</v>
       </c>
       <c r="H73" t="n">
-        <v>0.9999999996357465</v>
+        <v>8.295068526585129e-08</v>
       </c>
     </row>
     <row r="74">
@@ -2646,13 +2646,13 @@
         </is>
       </c>
       <c r="F74" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G74" t="n">
-        <v>8.779999999999999</v>
+        <v>13.22</v>
       </c>
       <c r="H74" t="n">
-        <v>7.913435684995362e-19</v>
+        <v>3.278334502453154e-40</v>
       </c>
     </row>
     <row r="75">
@@ -2676,13 +2676,13 @@
         </is>
       </c>
       <c r="F75" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G75" t="n">
-        <v>9.550000000000001</v>
+        <v>14.63</v>
       </c>
       <c r="H75" t="n">
-        <v>6.185997414781388e-22</v>
+        <v>8.667117886073779e-49</v>
       </c>
     </row>
     <row r="76">
@@ -2709,10 +2709,10 @@
         <v>1</v>
       </c>
       <c r="G76" t="n">
-        <v>-6.16</v>
+        <v>-1.12</v>
       </c>
       <c r="H76" t="n">
-        <v>0.9999999996357465</v>
+        <v>0.8688776250621797</v>
       </c>
     </row>
     <row r="77">
@@ -2736,13 +2736,13 @@
         </is>
       </c>
       <c r="F77" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G77" t="n">
-        <v>8.779999999999999</v>
+        <v>12.84</v>
       </c>
       <c r="H77" t="n">
-        <v>7.913435684995362e-19</v>
+        <v>4.901624287762901e-38</v>
       </c>
     </row>
     <row r="78">
@@ -2766,13 +2766,13 @@
         </is>
       </c>
       <c r="F78" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G78" t="n">
-        <v>9.550000000000001</v>
+        <v>14.16</v>
       </c>
       <c r="H78" t="n">
-        <v>6.185997414781388e-22</v>
+        <v>7.680509419697031e-46</v>
       </c>
     </row>
     <row r="79">
@@ -2799,10 +2799,10 @@
         <v>1</v>
       </c>
       <c r="G79" t="n">
-        <v>-6.16</v>
+        <v>-1.86</v>
       </c>
       <c r="H79" t="n">
-        <v>0.9999999996357465</v>
+        <v>0.968425237729363</v>
       </c>
     </row>
     <row r="80">
@@ -2826,13 +2826,13 @@
         </is>
       </c>
       <c r="F80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G80" t="n">
-        <v>8.779999999999999</v>
+        <v>12.63</v>
       </c>
       <c r="H80" t="n">
-        <v>7.913435684995362e-19</v>
+        <v>7.672675169567512e-37</v>
       </c>
     </row>
     <row r="81">
@@ -2856,13 +2856,13 @@
         </is>
       </c>
       <c r="F81" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G81" t="n">
-        <v>9.550000000000001</v>
+        <v>13.91</v>
       </c>
       <c r="H81" t="n">
-        <v>6.185997414781388e-22</v>
+        <v>2.949638939435252e-44</v>
       </c>
     </row>
     <row r="82">
@@ -2889,10 +2889,10 @@
         <v>1</v>
       </c>
       <c r="G82" t="n">
-        <v>-6.16</v>
+        <v>-2.29</v>
       </c>
       <c r="H82" t="n">
-        <v>0.9999999996357465</v>
+        <v>0.9888488923212675</v>
       </c>
     </row>
     <row r="83">
@@ -2916,13 +2916,13 @@
         </is>
       </c>
       <c r="F83" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G83" t="n">
-        <v>8.779999999999999</v>
+        <v>12.8</v>
       </c>
       <c r="H83" t="n">
-        <v>7.913435684995362e-19</v>
+        <v>8.085510895840641e-38</v>
       </c>
     </row>
     <row r="84">
@@ -2946,13 +2946,13 @@
         </is>
       </c>
       <c r="F84" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G84" t="n">
-        <v>9.550000000000001</v>
+        <v>14.12</v>
       </c>
       <c r="H84" t="n">
-        <v>6.185997414781388e-22</v>
+        <v>1.496308304539895e-45</v>
       </c>
     </row>
     <row r="85">
@@ -2979,10 +2979,10 @@
         <v>1</v>
       </c>
       <c r="G85" t="n">
-        <v>-6.16</v>
+        <v>-0.43</v>
       </c>
       <c r="H85" t="n">
-        <v>0.9999999996357465</v>
+        <v>0.6664212142711128</v>
       </c>
     </row>
     <row r="86">
@@ -3006,13 +3006,13 @@
         </is>
       </c>
       <c r="F86" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G86" t="n">
-        <v>8.779999999999999</v>
+        <v>11.96</v>
       </c>
       <c r="H86" t="n">
-        <v>7.913435684995362e-19</v>
+        <v>2.777684828555364e-33</v>
       </c>
     </row>
     <row r="87">
@@ -3036,13 +3036,13 @@
         </is>
       </c>
       <c r="F87" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G87" t="n">
-        <v>9.550000000000001</v>
+        <v>13.12</v>
       </c>
       <c r="H87" t="n">
-        <v>6.185997414781388e-22</v>
+        <v>1.245341382087627e-39</v>
       </c>
     </row>
     <row r="88">
@@ -3069,10 +3069,10 @@
         <v>1</v>
       </c>
       <c r="G88" t="n">
-        <v>-6.16</v>
+        <v>-1.84</v>
       </c>
       <c r="H88" t="n">
-        <v>0.9999999996357465</v>
+        <v>0.9670160070358848</v>
       </c>
     </row>
     <row r="89">
@@ -3096,13 +3096,13 @@
         </is>
       </c>
       <c r="F89" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G89" t="n">
-        <v>8.779999999999999</v>
+        <v>11.94</v>
       </c>
       <c r="H89" t="n">
-        <v>7.913435684995362e-19</v>
+        <v>3.553598464454482e-33</v>
       </c>
     </row>
     <row r="90">
@@ -3126,13 +3126,13 @@
         </is>
       </c>
       <c r="F90" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G90" t="n">
-        <v>9.550000000000001</v>
+        <v>13.1</v>
       </c>
       <c r="H90" t="n">
-        <v>6.185997414781388e-22</v>
+        <v>1.707742933631604e-39</v>
       </c>
     </row>
     <row r="91">
@@ -3159,10 +3159,10 @@
         <v>1</v>
       </c>
       <c r="G91" t="n">
-        <v>-6.16</v>
+        <v>-3.44</v>
       </c>
       <c r="H91" t="n">
-        <v>0.9999999996357465</v>
+        <v>0.9997043843163769</v>
       </c>
     </row>
     <row r="92">
@@ -3186,13 +3186,13 @@
         </is>
       </c>
       <c r="F92" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G92" t="n">
-        <v>8.779999999999999</v>
+        <v>12.04</v>
       </c>
       <c r="H92" t="n">
-        <v>7.913435684995362e-19</v>
+        <v>1.035484278634706e-33</v>
       </c>
     </row>
     <row r="93">
@@ -3216,13 +3216,13 @@
         </is>
       </c>
       <c r="F93" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G93" t="n">
-        <v>9.550000000000001</v>
+        <v>13.22</v>
       </c>
       <c r="H93" t="n">
-        <v>6.185997414781388e-22</v>
+        <v>3.50709704092896e-40</v>
       </c>
     </row>
     <row r="94">
@@ -3246,13 +3246,13 @@
         </is>
       </c>
       <c r="F94" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G94" t="n">
-        <v>-6.16</v>
+        <v>-6.21</v>
       </c>
       <c r="H94" t="n">
-        <v>0.9999999996357465</v>
+        <v>0.9999999997380885</v>
       </c>
     </row>
     <row r="95">
@@ -3276,13 +3276,13 @@
         </is>
       </c>
       <c r="F95" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G95" t="n">
-        <v>8.779999999999999</v>
+        <v>11.92</v>
       </c>
       <c r="H95" t="n">
-        <v>7.913435684995362e-19</v>
+        <v>4.545610860166666e-33</v>
       </c>
     </row>
     <row r="96">
@@ -3306,13 +3306,13 @@
         </is>
       </c>
       <c r="F96" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G96" t="n">
-        <v>9.550000000000001</v>
+        <v>13.07</v>
       </c>
       <c r="H96" t="n">
-        <v>6.185997414781388e-22</v>
+        <v>2.34086242505922e-39</v>
       </c>
     </row>
     <row r="97">
@@ -3336,13 +3336,13 @@
         </is>
       </c>
       <c r="F97" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G97" t="n">
-        <v>-6.16</v>
+        <v>-9.210000000000001</v>
       </c>
       <c r="H97" t="n">
-        <v>0.9999999996357465</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98">
@@ -3366,13 +3366,13 @@
         </is>
       </c>
       <c r="F98" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G98" t="n">
-        <v>8.779999999999999</v>
+        <v>11.9</v>
       </c>
       <c r="H98" t="n">
-        <v>7.913435684995362e-19</v>
+        <v>5.813715380165891e-33</v>
       </c>
     </row>
     <row r="99">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="F99" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G99" t="n">
-        <v>9.550000000000001</v>
+        <v>13.05</v>
       </c>
       <c r="H99" t="n">
-        <v>6.185997414781388e-22</v>
+        <v>3.20736502684768e-39</v>
       </c>
     </row>
     <row r="100">
@@ -3426,13 +3426,13 @@
         </is>
       </c>
       <c r="F100" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G100" t="n">
-        <v>-6.16</v>
+        <v>-5.8</v>
       </c>
       <c r="H100" t="n">
-        <v>0.9999999996357465</v>
+        <v>0.9999999967096895</v>
       </c>
     </row>
     <row r="101">
@@ -3456,13 +3456,13 @@
         </is>
       </c>
       <c r="F101" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G101" t="n">
-        <v>8.779999999999999</v>
+        <v>12.06</v>
       </c>
       <c r="H101" t="n">
-        <v>7.913435684995362e-19</v>
+        <v>8.088433431710091e-34</v>
       </c>
     </row>
     <row r="102">
@@ -3486,13 +3486,13 @@
         </is>
       </c>
       <c r="F102" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G102" t="n">
-        <v>9.550000000000001</v>
+        <v>13.24</v>
       </c>
       <c r="H102" t="n">
-        <v>6.185997414781388e-22</v>
+        <v>2.552192239745987e-40</v>
       </c>
     </row>
     <row r="103">
@@ -3519,10 +3519,10 @@
         <v>1</v>
       </c>
       <c r="G103" t="n">
-        <v>-6.16</v>
+        <v>-1.32</v>
       </c>
       <c r="H103" t="n">
-        <v>0.9999999996357465</v>
+        <v>0.9059973733869139</v>
       </c>
     </row>
     <row r="104">
@@ -3546,13 +3546,13 @@
         </is>
       </c>
       <c r="F104" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G104" t="n">
-        <v>8.779999999999999</v>
+        <v>11.98</v>
       </c>
       <c r="H104" t="n">
-        <v>7.913435684995362e-19</v>
+        <v>2.170879534477818e-33</v>
       </c>
     </row>
     <row r="105">
@@ -3576,13 +3576,13 @@
         </is>
       </c>
       <c r="F105" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G105" t="n">
-        <v>9.550000000000001</v>
+        <v>13.15</v>
       </c>
       <c r="H105" t="n">
-        <v>6.185997414781388e-22</v>
+        <v>9.077624832354591e-40</v>
       </c>
     </row>
     <row r="106">
@@ -3606,13 +3606,13 @@
         </is>
       </c>
       <c r="F106" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G106" t="n">
-        <v>-6.16</v>
+        <v>-6.29</v>
       </c>
       <c r="H106" t="n">
-        <v>0.9999999996357465</v>
+        <v>0.9999999998414651</v>
       </c>
     </row>
     <row r="107">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="F107" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G107" t="n">
-        <v>8.779999999999999</v>
+        <v>16.65</v>
       </c>
       <c r="H107" t="n">
-        <v>7.913435684995362e-19</v>
+        <v>1.515308610993689e-62</v>
       </c>
     </row>
     <row r="108">
@@ -3669,10 +3669,10 @@
         <v>1</v>
       </c>
       <c r="G108" t="n">
-        <v>9.550000000000001</v>
+        <v>21.84</v>
       </c>
       <c r="H108" t="n">
-        <v>6.185997414781388e-22</v>
+        <v>5.226182603103257e-106</v>
       </c>
     </row>
     <row r="109">
@@ -3699,10 +3699,10 @@
         <v>1</v>
       </c>
       <c r="G109" t="n">
-        <v>-6.16</v>
+        <v>3.62</v>
       </c>
       <c r="H109" t="n">
-        <v>0.9999999996357465</v>
+        <v>0.0001470634635697393</v>
       </c>
     </row>
     <row r="110">
@@ -3726,13 +3726,13 @@
         </is>
       </c>
       <c r="F110" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G110" t="n">
-        <v>8.779999999999999</v>
+        <v>12.06</v>
       </c>
       <c r="H110" t="n">
-        <v>7.913435684995362e-19</v>
+        <v>8.088433431710091e-34</v>
       </c>
     </row>
     <row r="111">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="F111" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G111" t="n">
-        <v>9.550000000000001</v>
+        <v>13.24</v>
       </c>
       <c r="H111" t="n">
-        <v>6.185997414781388e-22</v>
+        <v>2.552192239745987e-40</v>
       </c>
     </row>
     <row r="112">
@@ -3786,13 +3786,13 @@
         </is>
       </c>
       <c r="F112" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G112" t="n">
-        <v>-6.16</v>
+        <v>-5.64</v>
       </c>
       <c r="H112" t="n">
-        <v>0.9999999996357465</v>
+        <v>0.9999999916468519</v>
       </c>
     </row>
     <row r="113">
@@ -3816,13 +3816,13 @@
         </is>
       </c>
       <c r="F113" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G113" t="n">
-        <v>8.779999999999999</v>
+        <v>12.11</v>
       </c>
       <c r="H113" t="n">
-        <v>7.913435684995362e-19</v>
+        <v>4.933320230922744e-34</v>
       </c>
     </row>
     <row r="114">
@@ -3846,13 +3846,13 @@
         </is>
       </c>
       <c r="F114" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G114" t="n">
-        <v>9.550000000000001</v>
+        <v>13.29</v>
       </c>
       <c r="H114" t="n">
-        <v>6.185997414781388e-22</v>
+        <v>1.349914964600838e-40</v>
       </c>
     </row>
     <row r="115">
@@ -3879,10 +3879,10 @@
         <v>1</v>
       </c>
       <c r="G115" t="n">
-        <v>-6.16</v>
+        <v>-1.26</v>
       </c>
       <c r="H115" t="n">
-        <v>0.9999999996357465</v>
+        <v>0.8957078306313604</v>
       </c>
     </row>
     <row r="116">
@@ -3906,13 +3906,13 @@
         </is>
       </c>
       <c r="F116" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G116" t="n">
-        <v>8.779999999999999</v>
+        <v>12.15</v>
       </c>
       <c r="H116" t="n">
-        <v>7.913435684995362e-19</v>
+        <v>3.007446842758064e-34</v>
       </c>
     </row>
     <row r="117">
@@ -3936,13 +3936,13 @@
         </is>
       </c>
       <c r="F117" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G117" t="n">
-        <v>9.550000000000001</v>
+        <v>13.34</v>
       </c>
       <c r="H117" t="n">
-        <v>6.185997414781388e-22</v>
+        <v>7.128254307578785e-41</v>
       </c>
     </row>
     <row r="118">
@@ -3969,10 +3969,10 @@
         <v>1</v>
       </c>
       <c r="G118" t="n">
-        <v>-6.16</v>
+        <v>-1.24</v>
       </c>
       <c r="H118" t="n">
-        <v>0.9999999996357465</v>
+        <v>0.8918323466931256</v>
       </c>
     </row>
     <row r="119">
@@ -3996,13 +3996,13 @@
         </is>
       </c>
       <c r="F119" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G119" t="n">
-        <v>8.779999999999999</v>
+        <v>12.09</v>
       </c>
       <c r="H119" t="n">
-        <v>7.913435684995362e-19</v>
+        <v>6.317268952481736e-34</v>
       </c>
     </row>
     <row r="120">
@@ -4026,13 +4026,13 @@
         </is>
       </c>
       <c r="F120" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G120" t="n">
-        <v>9.550000000000001</v>
+        <v>13.26</v>
       </c>
       <c r="H120" t="n">
-        <v>6.185997414781388e-22</v>
+        <v>1.856519552323369e-40</v>
       </c>
     </row>
     <row r="121">
@@ -4056,13 +4056,13 @@
         </is>
       </c>
       <c r="F121" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G121" t="n">
-        <v>-6.16</v>
+        <v>-5.85</v>
       </c>
       <c r="H121" t="n">
-        <v>0.9999999996357465</v>
+        <v>0.9999999976092008</v>
       </c>
     </row>
     <row r="122">
@@ -4086,13 +4086,13 @@
         </is>
       </c>
       <c r="F122" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G122" t="n">
-        <v>8.779999999999999</v>
+        <v>16.75</v>
       </c>
       <c r="H122" t="n">
-        <v>7.913435684995362e-19</v>
+        <v>2.776391257223064e-63</v>
       </c>
     </row>
     <row r="123">
@@ -4119,10 +4119,10 @@
         <v>1</v>
       </c>
       <c r="G123" t="n">
-        <v>9.550000000000001</v>
+        <v>22.34</v>
       </c>
       <c r="H123" t="n">
-        <v>6.185997414781388e-22</v>
+        <v>6.84153436321791e-111</v>
       </c>
     </row>
     <row r="124">
@@ -4149,10 +4149,10 @@
         <v>1</v>
       </c>
       <c r="G124" t="n">
-        <v>-6.16</v>
+        <v>3.47</v>
       </c>
       <c r="H124" t="n">
-        <v>0.9999999996357465</v>
+        <v>0.0002580122559098581</v>
       </c>
     </row>
     <row r="125">
@@ -4176,13 +4176,13 @@
         </is>
       </c>
       <c r="F125" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G125" t="n">
-        <v>8.779999999999999</v>
+        <v>12.31</v>
       </c>
       <c r="H125" t="n">
-        <v>7.913435684995362e-19</v>
+        <v>4.134510806246516e-35</v>
       </c>
     </row>
     <row r="126">
@@ -4206,13 +4206,13 @@
         </is>
       </c>
       <c r="F126" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G126" t="n">
-        <v>9.550000000000001</v>
+        <v>13.53</v>
       </c>
       <c r="H126" t="n">
-        <v>6.185997414781388e-22</v>
+        <v>5.452009279446798e-42</v>
       </c>
     </row>
     <row r="127">
@@ -4239,10 +4239,10 @@
         <v>1</v>
       </c>
       <c r="G127" t="n">
-        <v>-6.16</v>
+        <v>-1.07</v>
       </c>
       <c r="H127" t="n">
-        <v>0.9999999996357465</v>
+        <v>0.858071356171467</v>
       </c>
     </row>
     <row r="128">
@@ -4266,13 +4266,13 @@
         </is>
       </c>
       <c r="F128" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G128" t="n">
-        <v>8.779999999999999</v>
+        <v>12.29</v>
       </c>
       <c r="H128" t="n">
-        <v>7.913435684995362e-19</v>
+        <v>5.300427916690601e-35</v>
       </c>
     </row>
     <row r="129">
@@ -4296,13 +4296,13 @@
         </is>
       </c>
       <c r="F129" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G129" t="n">
-        <v>9.550000000000001</v>
+        <v>13.5</v>
       </c>
       <c r="H129" t="n">
-        <v>6.185997414781388e-22</v>
+        <v>7.528904761747186e-42</v>
       </c>
     </row>
     <row r="130">
@@ -4329,10 +4329,10 @@
         <v>1</v>
       </c>
       <c r="G130" t="n">
-        <v>-6.16</v>
+        <v>-1.05</v>
       </c>
       <c r="H130" t="n">
-        <v>0.9999999996357465</v>
+        <v>0.8539743373974844</v>
       </c>
     </row>
     <row r="131">
@@ -4356,13 +4356,13 @@
         </is>
       </c>
       <c r="F131" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G131" t="n">
-        <v>8.779999999999999</v>
+        <v>12.27</v>
       </c>
       <c r="H131" t="n">
-        <v>7.913435684995362e-19</v>
+        <v>6.794422257579793e-35</v>
       </c>
     </row>
     <row r="132">
@@ -4386,13 +4386,13 @@
         </is>
       </c>
       <c r="F132" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G132" t="n">
-        <v>9.550000000000001</v>
+        <v>13.48</v>
       </c>
       <c r="H132" t="n">
-        <v>6.185997414781388e-22</v>
+        <v>1.039272996259214e-41</v>
       </c>
     </row>
     <row r="133">
@@ -4416,13 +4416,13 @@
         </is>
       </c>
       <c r="F133" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G133" t="n">
-        <v>-6.16</v>
+        <v>-4.92</v>
       </c>
       <c r="H133" t="n">
-        <v>0.9999999996357465</v>
+        <v>0.9999995685564298</v>
       </c>
     </row>
     <row r="134">
@@ -4446,13 +4446,13 @@
         </is>
       </c>
       <c r="F134" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G134" t="n">
-        <v>8.779999999999999</v>
+        <v>12.25</v>
       </c>
       <c r="H134" t="n">
-        <v>7.913435684995362e-19</v>
+        <v>8.708591524712528e-35</v>
       </c>
     </row>
     <row r="135">
@@ -4476,13 +4476,13 @@
         </is>
       </c>
       <c r="F135" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G135" t="n">
-        <v>9.550000000000001</v>
+        <v>13.46</v>
       </c>
       <c r="H135" t="n">
-        <v>6.185997414781388e-22</v>
+        <v>1.434002553238883e-41</v>
       </c>
     </row>
     <row r="136">
@@ -4506,13 +4506,13 @@
         </is>
       </c>
       <c r="F136" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G136" t="n">
-        <v>-6.16</v>
+        <v>-4.78</v>
       </c>
       <c r="H136" t="n">
-        <v>0.9999999996357465</v>
+        <v>0.9999991263519383</v>
       </c>
     </row>
     <row r="137">
@@ -4536,13 +4536,13 @@
         </is>
       </c>
       <c r="F137" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G137" t="n">
-        <v>8.779999999999999</v>
+        <v>12.25</v>
       </c>
       <c r="H137" t="n">
-        <v>7.913435684995362e-19</v>
+        <v>8.799376930483433e-35</v>
       </c>
     </row>
     <row r="138">
@@ -4566,13 +4566,13 @@
         </is>
       </c>
       <c r="F138" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G138" t="n">
-        <v>9.550000000000001</v>
+        <v>13.45</v>
       </c>
       <c r="H138" t="n">
-        <v>6.185997414781388e-22</v>
+        <v>1.450231683532798e-41</v>
       </c>
     </row>
     <row r="139">
@@ -4599,10 +4599,10 @@
         <v>1</v>
       </c>
       <c r="G139" t="n">
-        <v>-6.16</v>
+        <v>-4.41</v>
       </c>
       <c r="H139" t="n">
-        <v>0.9999999996357465</v>
+        <v>0.9999947860290382</v>
       </c>
     </row>
     <row r="140">
@@ -4626,13 +4626,13 @@
         </is>
       </c>
       <c r="F140" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G140" t="n">
-        <v>8.779999999999999</v>
+        <v>12.13</v>
       </c>
       <c r="H140" t="n">
-        <v>7.913435684995362e-19</v>
+        <v>3.891943416344342e-34</v>
       </c>
     </row>
     <row r="141">
@@ -4656,13 +4656,13 @@
         </is>
       </c>
       <c r="F141" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G141" t="n">
-        <v>9.550000000000001</v>
+        <v>13.31</v>
       </c>
       <c r="H141" t="n">
-        <v>6.185997414781388e-22</v>
+        <v>9.921342165056824e-41</v>
       </c>
     </row>
     <row r="142">
@@ -4689,10 +4689,10 @@
         <v>1</v>
       </c>
       <c r="G142" t="n">
-        <v>-6.16</v>
+        <v>-0.89</v>
       </c>
       <c r="H142" t="n">
-        <v>0.9999999996357465</v>
+        <v>0.8145697767824955</v>
       </c>
     </row>
     <row r="143">
@@ -4716,13 +4716,13 @@
         </is>
       </c>
       <c r="F143" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G143" t="n">
-        <v>8.779999999999999</v>
+        <v>12.19</v>
       </c>
       <c r="H143" t="n">
-        <v>7.913435684995362e-19</v>
+        <v>1.85155162571227e-34</v>
       </c>
     </row>
     <row r="144">
@@ -4746,13 +4746,13 @@
         </is>
       </c>
       <c r="F144" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G144" t="n">
-        <v>9.550000000000001</v>
+        <v>13.38</v>
       </c>
       <c r="H144" t="n">
-        <v>6.185997414781388e-22</v>
+        <v>3.800205705889698e-41</v>
       </c>
     </row>
     <row r="145">
@@ -4776,13 +4776,13 @@
         </is>
       </c>
       <c r="F145" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G145" t="n">
-        <v>-6.16</v>
+        <v>-4</v>
       </c>
       <c r="H145" t="n">
-        <v>0.9999999996357465</v>
+        <v>0.9999677885850962</v>
       </c>
     </row>
     <row r="146">
@@ -4806,13 +4806,13 @@
         </is>
       </c>
       <c r="F146" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G146" t="n">
-        <v>8.779999999999999</v>
+        <v>12.23</v>
       </c>
       <c r="H146" t="n">
-        <v>7.913435684995362e-19</v>
+        <v>1.127706248858515e-34</v>
       </c>
     </row>
     <row r="147">
@@ -4836,13 +4836,13 @@
         </is>
       </c>
       <c r="F147" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G147" t="n">
-        <v>9.550000000000001</v>
+        <v>13.43</v>
       </c>
       <c r="H147" t="n">
-        <v>6.185997414781388e-22</v>
+        <v>2.000198341425878e-41</v>
       </c>
     </row>
     <row r="148">
@@ -4869,10 +4869,10 @@
         <v>1</v>
       </c>
       <c r="G148" t="n">
-        <v>-6.16</v>
+        <v>-1.34</v>
       </c>
       <c r="H148" t="n">
-        <v>0.9999999996357465</v>
+        <v>0.9106032872533252</v>
       </c>
     </row>
     <row r="149">
@@ -4896,13 +4896,13 @@
         </is>
       </c>
       <c r="F149" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G149" t="n">
-        <v>8.779999999999999</v>
+        <v>12.12</v>
       </c>
       <c r="H149" t="n">
-        <v>7.913435684995362e-19</v>
+        <v>4.255744864925681e-34</v>
       </c>
     </row>
     <row r="150">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="F150" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G150" t="n">
-        <v>9.550000000000001</v>
+        <v>13.29</v>
       </c>
       <c r="H150" t="n">
-        <v>6.185997414781388e-22</v>
+        <v>1.328588846328207e-40</v>
       </c>
     </row>
     <row r="151">
@@ -4959,10 +4959,10 @@
         <v>1</v>
       </c>
       <c r="G151" t="n">
-        <v>-6.16</v>
+        <v>-0.29</v>
       </c>
       <c r="H151" t="n">
-        <v>0.9999999996357465</v>
+        <v>0.6157320480358301</v>
       </c>
     </row>
     <row r="152">
@@ -4986,13 +4986,13 @@
         </is>
       </c>
       <c r="F152" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G152" t="n">
-        <v>8.779999999999999</v>
+        <v>16.61</v>
       </c>
       <c r="H152" t="n">
-        <v>7.913435684995362e-19</v>
+        <v>3.121603174999496e-62</v>
       </c>
     </row>
     <row r="153">
@@ -5016,13 +5016,13 @@
         </is>
       </c>
       <c r="F153" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G153" t="n">
-        <v>9.550000000000001</v>
+        <v>21.47</v>
       </c>
       <c r="H153" t="n">
-        <v>6.185997414781388e-22</v>
+        <v>1.649825643543809e-102</v>
       </c>
     </row>
     <row r="154">
@@ -5049,10 +5049,10 @@
         <v>1</v>
       </c>
       <c r="G154" t="n">
-        <v>-6.16</v>
+        <v>2.74</v>
       </c>
       <c r="H154" t="n">
-        <v>0.9999999996357465</v>
+        <v>0.003069198985353583</v>
       </c>
     </row>
     <row r="155">
@@ -5076,13 +5076,13 @@
         </is>
       </c>
       <c r="F155" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G155" t="n">
-        <v>8.779999999999999</v>
+        <v>16.51</v>
       </c>
       <c r="H155" t="n">
-        <v>7.913435684995362e-19</v>
+        <v>1.527711043823019e-61</v>
       </c>
     </row>
     <row r="156">
@@ -5106,13 +5106,13 @@
         </is>
       </c>
       <c r="F156" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G156" t="n">
-        <v>9.550000000000001</v>
+        <v>21.04</v>
       </c>
       <c r="H156" t="n">
-        <v>6.185997414781388e-22</v>
+        <v>1.519761384142543e-98</v>
       </c>
     </row>
     <row r="157">
@@ -5139,10 +5139,10 @@
         <v>1</v>
       </c>
       <c r="G157" t="n">
-        <v>-6.16</v>
+        <v>2.66</v>
       </c>
       <c r="H157" t="n">
-        <v>0.9999999996357465</v>
+        <v>0.003957946055088788</v>
       </c>
     </row>
     <row r="158">
@@ -5166,13 +5166,13 @@
         </is>
       </c>
       <c r="F158" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G158" t="n">
-        <v>8.779999999999999</v>
+        <v>16.35</v>
       </c>
       <c r="H158" t="n">
-        <v>7.913435684995362e-19</v>
+        <v>2.295872874537167e-60</v>
       </c>
     </row>
     <row r="159">
@@ -5196,13 +5196,13 @@
         </is>
       </c>
       <c r="F159" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G159" t="n">
-        <v>9.550000000000001</v>
+        <v>20.37</v>
       </c>
       <c r="H159" t="n">
-        <v>6.185997414781388e-22</v>
+        <v>1.605343023801674e-92</v>
       </c>
     </row>
     <row r="160">
@@ -5229,10 +5229,10 @@
         <v>1</v>
       </c>
       <c r="G160" t="n">
-        <v>-6.16</v>
+        <v>2.51</v>
       </c>
       <c r="H160" t="n">
-        <v>0.9999999996357465</v>
+        <v>0.006089825948654949</v>
       </c>
     </row>
     <row r="161">
@@ -5256,13 +5256,13 @@
         </is>
       </c>
       <c r="F161" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G161" t="n">
-        <v>8.779999999999999</v>
+        <v>16.6</v>
       </c>
       <c r="H161" t="n">
-        <v>7.913435684995362e-19</v>
+        <v>3.679001962224814e-62</v>
       </c>
     </row>
     <row r="162">
@@ -5286,13 +5286,13 @@
         </is>
       </c>
       <c r="F162" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G162" t="n">
-        <v>9.550000000000001</v>
+        <v>21.4</v>
       </c>
       <c r="H162" t="n">
-        <v>6.185997414781388e-22</v>
+        <v>6.516519464237575e-102</v>
       </c>
     </row>
     <row r="163">
@@ -5319,10 +5319,10 @@
         <v>1</v>
       </c>
       <c r="G163" t="n">
-        <v>-6.16</v>
+        <v>2.8</v>
       </c>
       <c r="H163" t="n">
-        <v>0.9999999996357465</v>
+        <v>0.00254901995807051</v>
       </c>
     </row>
     <row r="164">
@@ -5346,13 +5346,13 @@
         </is>
       </c>
       <c r="F164" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G164" t="n">
-        <v>8.779999999999999</v>
+        <v>16.09</v>
       </c>
       <c r="H164" t="n">
-        <v>7.913435684995362e-19</v>
+        <v>1.43893422026927e-58</v>
       </c>
     </row>
     <row r="165">
@@ -5376,13 +5376,13 @@
         </is>
       </c>
       <c r="F165" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G165" t="n">
-        <v>9.550000000000001</v>
+        <v>19.49</v>
       </c>
       <c r="H165" t="n">
-        <v>6.185997414781388e-22</v>
+        <v>7.318936257895339e-85</v>
       </c>
     </row>
     <row r="166">
@@ -5409,10 +5409,10 @@
         <v>1</v>
       </c>
       <c r="G166" t="n">
-        <v>-6.16</v>
+        <v>2.39</v>
       </c>
       <c r="H166" t="n">
-        <v>0.9999999996357465</v>
+        <v>0.008369145135534597</v>
       </c>
     </row>
     <row r="167">
@@ -5436,13 +5436,13 @@
         </is>
       </c>
       <c r="F167" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G167" t="n">
-        <v>8.779999999999999</v>
+        <v>15.83</v>
       </c>
       <c r="H167" t="n">
-        <v>7.913435684995362e-19</v>
+        <v>9.260902456062847e-57</v>
       </c>
     </row>
     <row r="168">
@@ -5466,13 +5466,13 @@
         </is>
       </c>
       <c r="F168" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G168" t="n">
-        <v>9.550000000000001</v>
+        <v>18.73</v>
       </c>
       <c r="H168" t="n">
-        <v>6.185997414781388e-22</v>
+        <v>1.322747606939585e-78</v>
       </c>
     </row>
     <row r="169">
@@ -5499,10 +5499,10 @@
         <v>1</v>
       </c>
       <c r="G169" t="n">
-        <v>-6.16</v>
+        <v>2.17</v>
       </c>
       <c r="H169" t="n">
-        <v>0.9999999996357465</v>
+        <v>0.01490881577100626</v>
       </c>
     </row>
     <row r="170">
@@ -5526,13 +5526,13 @@
         </is>
       </c>
       <c r="F170" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G170" t="n">
-        <v>8.779999999999999</v>
+        <v>15.47</v>
       </c>
       <c r="H170" t="n">
-        <v>7.913435684995362e-19</v>
+        <v>2.629131839566386e-54</v>
       </c>
     </row>
     <row r="171">
@@ -5556,13 +5556,13 @@
         </is>
       </c>
       <c r="F171" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G171" t="n">
-        <v>9.550000000000001</v>
+        <v>17.89</v>
       </c>
       <c r="H171" t="n">
-        <v>6.185997414781388e-22</v>
+        <v>6.576862265712339e-72</v>
       </c>
     </row>
     <row r="172">
@@ -5589,10 +5589,10 @@
         <v>1</v>
       </c>
       <c r="G172" t="n">
-        <v>-6.16</v>
+        <v>1.81</v>
       </c>
       <c r="H172" t="n">
-        <v>0.9999999996357465</v>
+        <v>0.03502982115945793</v>
       </c>
     </row>
     <row r="173">
@@ -5616,13 +5616,13 @@
         </is>
       </c>
       <c r="F173" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G173" t="n">
-        <v>8.779999999999999</v>
+        <v>15.99</v>
       </c>
       <c r="H173" t="n">
-        <v>7.913435684995362e-19</v>
+        <v>7.793721118273408e-58</v>
       </c>
     </row>
     <row r="174">
@@ -5646,13 +5646,13 @@
         </is>
       </c>
       <c r="F174" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G174" t="n">
-        <v>9.550000000000001</v>
+        <v>19.11</v>
       </c>
       <c r="H174" t="n">
-        <v>6.185997414781388e-22</v>
+        <v>9.601864928091332e-82</v>
       </c>
     </row>
     <row r="175">
@@ -5679,10 +5679,10 @@
         <v>1</v>
       </c>
       <c r="G175" t="n">
-        <v>-6.16</v>
+        <v>2.09</v>
       </c>
       <c r="H175" t="n">
-        <v>0.9999999996357465</v>
+        <v>0.01838043602443931</v>
       </c>
     </row>
   </sheetData>
